--- a/Book1 (1).xlsx
+++ b/Book1 (1).xlsx
@@ -425,166 +425,6540 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>spotify link</t>
+          <t>savan link</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NEW PLAYS September 01, 2025</t>
+          <t>Plays  September 28, 2025</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>Labels</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ARTISTS</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>LABELS</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TITLE</t>
+          <t>Artists</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/track/5NngmzhAt8aJtCmunFWRCh</t>
+          <t>https://www.jiosaavn.com/song/aaj/ki/raat/male/version/KSA0ZzJ6enk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1,015</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>© 2024 ℗ Manandabhagwati@gmail.com</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/track/7h3Pno1aFbHpFsoqzF0sLX</t>
+          <t>https://www.jiosaavn.com/song/jane/kyon/log/mohabbat/kiya/jhankar/beats/ORJeVkdRfmM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>© 2024 Pabitra Entertainment</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/track/4R9ecfTfS2BWCbgIn8zl9T</t>
+          <t>https://www.jiosaavn.com/song/kya/hua/tera/vada/KRwYSEBJeVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>© 2024 Inbox Tunes</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://open.spotify.com/track/5ZY6Tet68fX8ea0R0D80T5</t>
+          <t>https://www.jiosaavn.com/song/ek/haseena/thi/film/karz/1980/GDA5RUBHW1E</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>261,385</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Invalid URL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>© 2024 Merchant Records</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>None</t>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/ko/dekha/unplugged/Ox5eQBN9XFc</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ve/kamleya/unplugged/MyogYSNlXn4</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/the/ultimate/kishore/da/mashup/BQUYAkBlQwY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/pyar/ka/naghma/hai/IgBGBBpCcEY</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/inhin/logon/ne/remixed/by/jai/walia/ERwNeRBhVn8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/are/diwanon/mujhe/pehchano/FAtSRRx4Z0s</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bahut/pyaar/karte/hain/recreated/CiwmRQ5ZTVc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/achha/to/ham/chalte/hain/remix/Og8KYA1ddnw</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ka/karoon/sajni/MiwBUDIHbWw</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/na/jane/kis/jahan/men/kho/gaye/lofi/NT8dBDUFRwQ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/yeh/raat/yeh/chandni/reprise/MzdZZz1ffGM</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/na/tum/jano/na/hum/acoustic/RD07dS1AeGk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dheeme/dheeme/refresh/version/NlADBxB,WF8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ye/honsla/reprise/NzA4cjZKfAY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chhod/diya/lofi/FjkZcxkdaFY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/meri/kismat/mein/tu/nahin/shayad/jhankar/beats/GhAjejFkAmw</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/gali-mein-chand-amapiano-mix/OgwbBCsJfwM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>℗ 2024 Saregama India Ltd</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Gali Mein Chand - Amapiano Mix</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jammy Weirdo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chaudhvin/ka/chand/ho/AQAZRRBbXnE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tere-jeya-hor-disda/XQJbYhN4RFk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>42983</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>℗ 2021 Synk Records</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Tere Jeya Hor Disda</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Siddharth Slathia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/yeh/haseen/vadiyan/yeh/khula/aasman/jammin/AlAPfgFoD2U</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mujhe/ishq/hai/tujhi/se/jhankar/beats/PysNdARmX0M</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/o/mere/sona/re/sona/KSkef01pemY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/panna/ki/tamanna/hai/Aiw7YwAFRGI</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/woh/ladki/bahut/yaad/aati/hai/unplugged/MTgRRkVYQ0k</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/premam/jayati/QVpZBDxKRGc</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tera/dil/mere/paas/x/hum/nahi/tere/dushmano/mein/recreated/song/NSwoVTZEc1E</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/rahen/na/rahen/unplugged/E1pSQwV3ZgQ</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chup/chup/khade/ho/zaroor/koi/baat/hai/HxtGVStqR3A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/lekar/hum/deewana/dil/GA0ndkdzbWc</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/toota/jo/kabhi/tara/by/vaibhav/yadav/amrita/chimnani/EhAfdxF2UHE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bade/achhe/lagte/hain/unplugged/lofi/OwQcYSYHB3Y</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pardesi/pardesi/cover/version/cover/version/Qjw9dCJDRHQ</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aawaz/do/hamko/BlwBXCZ7eVc</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jeena/isi/ka/naam/hai/EhoBfD9dB10</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/choodi/nahin/yeh/mera/dil/hai/unwind/version/AB8xQhldQVg</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/likhe/jo/khat/tujhe/magic/moments/music/studio/season/1/MgslcyBgZ2w</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/rashke/qamar/recreated/version/SRlGdFlDdAc</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/gum/hai/kisi/ke/acoustic/OB9bfztCT3E</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/lambi/judaai/RRIMAwFiTnA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chappa/chappa/unwind/version/BSQdXhVZAkE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/rahen/na/rahen/ETpdBxxcdH8</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aap/ki/nazron/ne/samjha/IhwPeCZIVXU</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/mile/dil/khile/NiIDBCRoU1E</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/intaha/ho/gai/intezar/ki/HiwfQkVRWkA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/ladki/ko/dekha/KQ8tfh9,BVU</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/jaane/naa/cover/cover/version/cover/version/ADpdXBtBc0s</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chand/mera/dil/chandni/ho/tum/OD5SWhVnY0A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aawaz/do/humko/unplugged/RA8lfjxvU2k</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kaise/mein/kahun/tujhse/Rhg,AzlBfHE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/se/re/reprised/version/NTwiRkJWf34</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chura/liya/hai/I14/Bh5Rc3Q</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/zindagi/ban/gaye/ho/tum/OToNAhgGRws</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/hoom/hoom/kare/unwind/version/OC4fUENYXUU</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tere/dar/par/sanam/cover/version/cover/version/HQUfBEZxR3Y</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/main/tere/ishq/mein/FCkiUi4AYgI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jane/kyon/log/mohabbat/kiya/carvaan/lounge/IwAaXBtHRHg</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/goom/hai/kisi/ke/pyar/mein/GiEmRU1YYQo</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/humen/tumse/pyar/kitna/jalraj/chillwave/Pj5eXRZkQgc</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/beqarar/karke/hamen/yun/na/jaiye/JxEIXhBnVkY</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jaadu/hai/nasha/electrowind/SQYzUztEdUk</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jeena/yahan/RxAPXxJBAGM</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/meri/bheegi/bheegi/si/AVlddAZxfFE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aa/chal/ke/tujhe/RwUyZ1lZB2o</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/sambhala/hai/maine/take%c2%a02/EVwdfDpyRXg</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/jo/mil/gaye/ho/carvaan/lounge/JQwKCUdBWHg</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chitthi/na/koi/sandesh/jhankar/beats/FBsjUB5TYnQ</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hum/tum/se/pyar/na/karte/reprise/EVAAdDBEbgM</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/se/badhkar/duniya/mein/Ojc4d0R9R0k</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chaudhvin/ka/chand/ho/NicnYxZxBgU</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/sapnon/ki/rani/ASkgfBsEW2A</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jaadu/hai/nasha/hai/EgwsQUEJfUQ</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/door/kahin/naa/ja/zara/zara/reprise/Og07Wkd4Bnk</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/ko/dekha/to/yeh/khayal/aaya/FBszRUReQ1A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/rimjhim/gire/sawan/BzApfjtSfEM</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aur/is/dil/mein/ChkNbkZvAmw</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kya/hua/tera/vada/CScbdDpdUlc</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jab/koi/baat/lo/fi/NAImZg5jb3E</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/achha/ji/main/haari/unplugged/MVA/VyJ6Dgc</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/likhe/jo/khat/tujhe/CVwOVgF6Y1U</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/the/antakshari/mashup/KQszAzB5BlE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kya/hua/tera/wada/acoustic/SSIJeAd,XGU</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/mere/saamne/BD0idVkCZAU</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aawaz-do-humko-unplugged/FhgJeBpZUkQ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>17444</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>℗ 2023 Saregama India Ltd</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Aawaz Do Humko - Unplugged</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Rahul Jain</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aisa/sama/na/hota/RCIAXQUBVQM</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ruk/ja/o/dil/deewane/CFxfUAJ/U0Q</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/zindagi/ke/safar/mein/BjApWAQCfFo</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aur/is/dil/mein/lofi/KTodU0MCQEI</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tere/jaisa/yaar/kahan/SQYfUCt0XQY</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/zara/zara/Qi4HRAVTU3k</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/maula/mere/maula/HSsyeSRHdGE</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/kya/mile/siddharth/slathia/version/JCEnHBxBQGo</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/piya/tose/naina/laage/re/GiMfUyB/YEU</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/agar/mujhse/mohabbat/hai/reprise/JSExWytIAQQ</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/mehboob/qayamat/hogi/BxAmfSV9U1w</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kiss/me/baby/reprise/PyIbXTBjWUU</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/teri/galiyon/mein/CBIzCQB6aEY</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/sambhala/hai/maine/cover/version/cover/version/Fi0fBC5naHg</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pehla/pehla/pyaar/hai/SAteRjNZblg</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/o/haseena/STEcdhpUZlI</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kitna/bechain/hoke/reprise/JAEiZyVqD3k</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/saat/samundar/QQ4dYCJfWR4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/maine/dil/se/kaha/JwEleh0Bf1c</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bade/achhe/lagte/hain/unplugged/OyIpVSQAcUo</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/yeh/kya/hua/FQUzQkRDR2Y</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/parde/mein/rehne/do/EzgxehN3BGs</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/muskurane/ki/wajah/tum/ho/female/sad/version/IRxcBj1SXnA</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pyar/hua/chupke/se/HxhSS0ZzZng</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pehla/pehla/pyaar/hai/lofi/H14qXw57TX8</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ve/kamleya///siddharth/slathia/version/Qw4KWTFhQQo</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/phoolon/ke/rang/se/Kh8zRS0AcwQ</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kisi/pe/dil/agar/aa/jaye/to/KC8iAjNZfVc</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chalte/chalte/yun/hi/koi/FSUscCB4BHI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tumne/kisi/se/kabhi/pyar/kiya/hai/reprise/JSYBA0J4Qms</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pag/ghungroo/Ig8hASdDBXA</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/humen/tumse/pyar/kitna/jhankar/beats/Ej4OZzp2dnU</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/kehta/hai/to/chalun/recreated/ER0kVkB6Ymw</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jaanam/the/tabla/guy/cover/AS8OZUdaZ3w</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/rutha/to/Ri8kQBJ6RUM</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ehsan/tera/hoga/mujh/par/OBwmWAd0aEk</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/angane/mein/Fl0HcyBKfFI</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chalte/chalte/yun/hi/koi/RR4fbh1odFY</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jab/chhaye/GwYbZxdjA3s</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/akele/hai/chale/aao/unplugged/QF0yCQB7eHk</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/rehnaa/hai/tere/dil/mein/CTodYiUBc1c</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aji/rooth/kar/RT0qaTd2eHU</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ankhiyon/ke/jharokhon/se/HCMBcycHD18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/lag/ja/gale/jhankar/beats/SFlbWR1xYVQ</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/lambi/judaai/lofi/Hi5TQjpmRGo</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/mere/saamne/lofi/KFsufSIJeEo</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/awaarapan/banjarapan/SS4DVSRgBEQ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chura/liya/hai/tumne/MSkyCAV2Dnw</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/samnewali/khidki/mein/unplugged/KTAyXyF7QQQ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jo/wada/kiya/woh/nibhana/padega/SBtbeiIFdFY</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bade/achhe/lagte/hain/jhankar/beats/CgAZBQZ0elk</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jane/woh/kaise/log/the/HD4sAh9SQ2U</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/o/mere/dil/ke/chain/IiEFQEJcD1Q</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/none/none/NAkeUxV/ZwE</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hamari/atariya/LxkSdzdRW3w</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tujhe/dekha/toh/rap/mix/HiATeSYJcgY</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/na/tum/jano/na/hum/KAcmCUB/UgM</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/saiyan/dil/mein/aana/re/lofi/IzstYQB2UFY</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/dil/ki/dhadkan/mein/reprise/KREydSJSUno</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kahin/door/jab/din/dhal/jaye/QxFZHAFUW14</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ruk/jana/nahin/unplugged/Alw9ehp0bh4</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aankhon/se/tune/cover/version/cover/version/RTAMUAEIBgY</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ajib/dastan/hai/yeh/jhankar/beats/IjIlfkNlT10</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jahan/teri/yeh/nazar/hai/AhAlfkFYRVc</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/yeh/sham/mastani/Qj85UANDXmA</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/ajnabee/haseena/se/SSpcaSEDY1w</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hum/to/mohabbat/NyEkegRmWFI</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chingari/koi/bhadke/jhankar/beats/Il0jCBlzdQM</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bade/achhe/lagte/hain/afro/mix/SSldcCtlbnI</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/ajnabee/haseena/se/lofi/IQ0xRS15e30</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/do/lafzon/ki/hai/dil/ki/kahani/BCM7RDcAAGA</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kuchh/na/kaho/synthwave/PCUaBCRSWUo</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/naam/goom/jayega/MycISE0JA2M</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/pyar/ka/nagma/hai/chill/lofi/IlgjSSZkWGY</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mere/samnewali/khidki/mein/unplugged/HDcTVBxvTVg</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mera/saaya/acoustic/CjFZXUxnWXs</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tose/naina/lage/NgY,YwR/RXk</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/wada/karo/cover/version/QhAsdRV3AGs</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jeena/yahan/marna/yahan/JzE4WDxSWXQ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/maa/mahagauri/mantra/108/times/QCM0ZBwAcUI</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bekarar/karke/acoustic/LykAe0FefmE</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aaiye/meherbaan/acoustic/OxwmfDwIWQI</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pehla/nasha/HwcdRQNYQFs</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tujhe/dekha/to/HA05Zj14VWk</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/din/dhal/jaye/haye/Hy4CRzF3BR4</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jumma/chumma/RzgdRjMEBXk</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/eena-meena-deeka/El1ccj9mfnA</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>℗ 2025 Saregama India Ltd</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Eena Meena Deeka</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Hrutul</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hai/apna/dil/toh/aawara/acoustic/XQQxQR0dbks</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ehsan/tera/hoga/mujh/par/unplugged/KSUJVS1cY1o</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/mile/dil/khile/NioPejlxREE</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kehna/hai/acoustic/Ag0xAEdkGno</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hum-the-woh-thi/OiwFSwRiemk</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2893</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>℗ 2025 Saregama India Ltd</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Hum The Woh Thi</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Rajdeep Ghosh</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ankhiyon/ke/jharokhon/se/OhsYYSV3Zmw</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tujhse/naraz/nahi/lofi/flip/QS0MeR1Eelg</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/rim/jhim/rim/jhim/ASIdfDJXW38</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ye/samaa/GxAfBEdSVGs</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ya/devi/sarvbhuteshu/HzIoWhFcDnU</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ehsaan/tera/hoga/mujhpar/acoustic/IwkxAi5pD3o</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/bheed/mein/OywgWUFvf2I</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kombadi/palali/OyoBSDV6WGs</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/raat/kali/ek/khwab/men/aayi/unplugged/NwpZaCNkbVA</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dekha/hai/teri/aankhon/ko/cover/version/BhknekwJUQI</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kuch/na/kaho/unplugged/KSMySUxgcVE</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/nigahen/milane/ko/jee/chahta/hai/M14tQ0ZVaEE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dilko/tumse/pyar/hua/lofi/reverb/OS8hXQIFYnQ</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kabhi/main/kahoon/acapella/KVssYUBAeGY</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tu/mile/AQlSARNkWl0</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/awaarapan/banjarapan/lofi/QjoyAAxaR2I</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/teri/chunariya/cover/version/cover/version/BBkqbitoRko</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aap/ki/nazron/ne/samjha/QjBfWllcYX8</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek-pyaar-ka-nagma-hain/MysMBgJ8AUs</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>© 2021 Saregama</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Ek Pyaar Ka Nagma Hain</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Kavita Seth</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/masti/ki/paathshala/jammin/Qj8,YiBmW3o</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/kehta/hai/lo/fi/FiVGBD1AcQI</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/puchho/na/yaar/kya/hua/cover/version/FBscYBZHe0c</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mohabbat/ho/na/jaye/JTsEVB9ddGE</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aur/iss/dil/mein/PgVYXBpZfwo</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/nindiya/cover/version/ExpeYhtqQ0A</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/gore/gore/o/banke/chhore/IgQef0RiemU</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/waqt/ne/kiya/kya/haseen/sitam/JiAkcD8BTUo</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kahin/door/jab/din/dhal/jaye/NjIxaBcBGnA</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/gaata/rahe/mera/dil/PS0fCRZHTwA</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chand/si/mehbooba/ho/meri/KiMdZkJ0WH8</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ho/gaya/hai/tujhko/toh/pyar/sajana/CEU9Q0ZRYnw</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/achchi/lagti/ho/ADc5XRZfTkI</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tere/bina/zindagi/se/acoustic/EQEffFlcQUA</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ajib/dastaan/RTIOAwRnfws</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aajkal/tere/mere/pyar/ke/charche/O0VdU0MFR0M</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/o/saathi/re/M1weSD9qREQ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tujhse/naraz/nahi/siddharth/slathia/version/Rlg0dwIIfGM</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/pukarta/chala/hoon/main/acoustic/KRsHU1lJDgY</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/ek/ajnabee/haseena/se/CFENWRNjXV8</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/yara/seeli/seeli/Cj8sRzpadUo</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/na/tum/hamen/jano/BV8Ae0FXTgs</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dekha/jo/tumko/NR0FUgV9bwA</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/to/hai/dil/IlgRfQxBcmY</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jadoo/bhari/GhEoSSZVQ2U</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/meri/bheegi/bheegi/si/MSomHC1mc2A</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/khoya/khoya/chand/Oyw7fTx9WFI</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/mera/naam/chin/chin/chu/acoustic/QAMsCBFhUFY</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jab/hum/jawan/honge/HwwzWx97fGQ</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/aanewala/pal/janewala/hai/HRgnBkRic3U</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/roop/tera/acoustic/GiIleDF2cUY</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/raat/kali/ek/khwab/men/aai/NwQzAkRzXV0</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/tum/jo/mil/gaye/ho/M14YQ0AJZ1k</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/kahi/door/jab/din/dhal/acoustic/KCozXBFxTl0</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/woh/humse/khafa/hain/PDsDHEJ/TWY</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/suhana/safar/acoustic/RQE8QBFGb30</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/jo/haal/dil/ka/cover/version/cover/version/HFEhfBsDXF8</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chori/se/recreated/by/leslie/lewis/EVEgRQ5RXlI</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/dil/cheez/kya/hai/NT0jejF7YAM</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/hai/apna/dil/to/aawara/CQ0vCDNCfVo</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/chaudhvin/ka/chand/ho/QSRdfg5zbQU</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/lambi/judaai/unplugged/SSpbQxpZX3U</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>https://www.jiosaavn.com/song/humein/tumse/pyar/lofi/HDIxVxhRWFg</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Invalid URL</t>
         </is>
       </c>
     </row>
